--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(s2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(s2).xlsx
@@ -12,7 +12,7 @@
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="圣诺汀之梦_盖亚之心（索菲亚线下）" sheetId="1" r:id="rId1"/>
+    <sheet name="圣诺汀之梦_盖亚之心（索菲亚线下） (1)" sheetId="1" r:id="rId1"/>
     <sheet name="转换说明" sheetId="2" r:id="rId2"/>
     <sheet name="命令库" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="510">
   <si>
     <t>ID</t>
   </si>
@@ -255,7 +255,7 @@
     <t>火焰燃烧起来，从赴死之人的血液中升腾，先是吞掉了那片柔软的鳞翅，然后又裹着飞蛾消散的微光舔过盖曼的衣襟。</t>
   </si>
   <si>
-    <t>playsfx(FireIgnite)&amp;bgfade(sntzm_gy(s2)_17,1)</t>
+    <t>parallel(playsfx(FireIgnite);bgfade(sntzm_gy(s2)_17,1))</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=16</t>
@@ -357,42 +357,33 @@
     <t>源类型=type:txt_pb; 层级=26</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>你出声唤他的名字，大卫却对此充耳不闻，只是站在那里垂着头，看着地面上跳动的火光倒影，手指无意识地摩挲着右肩那片早已凝固的深色印记。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=27</t>
-  </si>
-  <si>
     <t>29</t>
   </si>
   <si>
     <t>大卫！你疯了吗？这片火焰是盖曼梦境崩解的表现，再不离开我们都只能留下来和他陪葬！</t>
   </si>
   <si>
-    <t>源类型=type:txt_You; 层级=28</t>
+    <t>源类型=type:txt_You; 层级=27</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>大卫站在离你们几步远的位置，目光正落在那片火焰上方，像是盯着某个正在缓慢成形的东西。</t>
+    <t>只见他站在离你们几步远的位置，目光正落在那片火焰上方，像是盯着某个正在缓慢成形的东西。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=28</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>火焰的光在他侧脸上投下明暗交错的轮廓，他肩膀在听到你的声音后朝你的方向微微偏了偏，声音隔着一层跳动的火幕，被烈焰燃烧的爆裂声割裂得支离破碎。</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=29</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>火焰的光在他侧脸上投下明暗交错的轮廓，他肩膀在听到你的声音后朝你的方向微微偏了偏，声音隔着一层跳动的火幕，被烈焰燃烧的爆裂声割裂得支离破碎。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=30</t>
-  </si>
-  <si>
     <t>32</t>
   </si>
   <si>
@@ -408,7 +399,7 @@
     <t>charfadein(L,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_David; 层级=31</t>
+    <t>源类型=type:txt_David; 层级=30</t>
   </si>
   <si>
     <t>33</t>
@@ -417,7 +408,7 @@
     <t>你愣在原地，一时以为是自己听错了。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=32</t>
+    <t>源类型=type:txt_pb; 层级=31</t>
   </si>
   <si>
     <t>34</t>
@@ -426,7 +417,7 @@
     <t>那家伙还在这里，在我的身体里。</t>
   </si>
   <si>
-    <t>源类型=type:txt_David; 层级=33</t>
+    <t>源类型=type:txt_David; 层级=32</t>
   </si>
   <si>
     <t>35</t>
@@ -438,7 +429,7 @@
     <t>charfadeout(L,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=34</t>
+    <t>源类型=type:txt_pb; 层级=33</t>
   </si>
   <si>
     <t>36</t>
@@ -453,7 +444,7 @@
     <t>别说胡话了，大卫。你知道我们不可能丢下你一个人。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Clark; 层级=35</t>
+    <t>源类型=type:txt_Clark; 层级=34</t>
   </si>
   <si>
     <t>37</t>
@@ -465,7 +456,7 @@
     <t>parallel(charfadeout(L,1);charfadein(R,1))</t>
   </si>
   <si>
-    <t>源类型=type:txt_David; 层级=36</t>
+    <t>源类型=type:txt_David; 层级=35</t>
   </si>
   <si>
     <t>38</t>
@@ -477,40 +468,40 @@
     <t>charfadeout(R,1)&amp;bgfade(sntzm_gy(s2)_38,1)</t>
   </si>
   <si>
+    <t>源类型=type:txt_pb; 层级=36</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>“Bang！”</t>
+  </si>
+  <si>
+    <t>playsfx(GunShot)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=37</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>“Bang！”</t>
-  </si>
-  <si>
-    <t>playsfx(GunShot)</t>
+    <t>40</t>
+  </si>
+  <si>
+    <t>只见一颗子弹呼啸着射向了克拉克所在的那台造梦设备，落点不偏不倚地打在了那颗红色的启动按钮上。只见一颗子弹呼啸着射向了克拉克所在的那台造梦设备，落点不偏不倚地打在了那颗红色的启动按钮上。</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_gy(s2)_40,1)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=38</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>只见一颗子弹呼啸着射向了克拉克所在的那台造梦设备，落点不偏不倚地打在了那颗红色的启动按钮上。只见一颗子弹呼啸着射向了克拉克所在的那台造梦设备，落点不偏不倚地打在了那颗红色的启动按钮上。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_gy(s2)_40,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=39</t>
-  </si>
-  <si>
     <t>41</t>
   </si>
   <si>
     <t>不......！</t>
   </si>
   <si>
-    <t>源类型=type:txt_Clark; 层级=40</t>
+    <t>源类型=type:txt_Clark; 层级=39</t>
   </si>
   <si>
     <t>42</t>
@@ -519,25 +510,25 @@
     <t>已经戴上头盔的克拉克还没来得及发出一声惊呼，意识就已经像冲马桶一样，被设备强行拽入了返回现实的隧道。</t>
   </si>
   <si>
+    <t>源类型=type:txt_pb; 层级=40</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>你看着突然发生的一切，脑子嗡嗡作响，完全无法理解已经到了最后的关头，为什么大卫突然做出这样的决定。</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=41</t>
   </si>
   <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>你看着突然发生的一切，脑子嗡嗡作响，完全无法理解已经到了最后的关头，为什么大卫突然做出这样的决定。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=42</t>
-  </si>
-  <si>
     <t>44</t>
   </si>
   <si>
     <t>果然......</t>
   </si>
   <si>
-    <t>源类型=type:txt_David; 层级=43</t>
+    <t>源类型=type:txt_David; 层级=42</t>
   </si>
   <si>
     <t>45</t>
@@ -546,7 +537,7 @@
     <t>他抬起枪口放在手里端详，拇指摩挲着冰凉的枪身，表情中没有欣喜，只有一种确认了什么事情后的蓦然的平静。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=44</t>
+    <t>源类型=type:txt_pb; 层级=43</t>
   </si>
   <si>
     <t>46</t>
@@ -555,7 +546,7 @@
     <t>就连我也拥有了一部分控制梦境的权限，换做平时这一枪是肯定打不中的。</t>
   </si>
   <si>
-    <t>源类型=type:txt_David; 层级=45</t>
+    <t>源类型=type:txt_David; 层级=44</t>
   </si>
   <si>
     <t>47</t>
@@ -564,7 +555,7 @@
     <t>他自言自语道，然后把枪口对准了你们两人。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=46</t>
+    <t>源类型=type:txt_pb; 层级=45</t>
   </si>
   <si>
     <t>48</t>
@@ -573,7 +564,13 @@
     <t>这就是为什么我说自己不能离开，亚当。他一直在我体内，他从一开始就没有真正想过要接受自己的死亡。</t>
   </si>
   <si>
-    <t>源类型=type:txt_David; 层级=47</t>
+    <t>源类型=type:txt_David; 层级=46</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>源类型=type:exeBC; 层级=47</t>
   </si>
   <si>
     <t>49</t>
@@ -915,13 +912,19 @@
     <t>源类型=type:txt_Abaddon; 层级=81</t>
   </si>
   <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>源类型=type:exeBC; 层级=82</t>
+  </si>
+  <si>
     <t>87</t>
   </si>
   <si>
     <t>当你的死讯传出，当初因你而陷入不幸的仇家只会认为你罪有应得。至于那些曾经让你做过假报道的公司和企业，他们只会松一口气，权当世上又少了一个知道他们肮脏秘密的麻烦。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Abaddon; 层级=82</t>
+    <t>源类型=type:txt_Abaddon; 层级=83</t>
   </si>
   <si>
     <t>88</t>
@@ -930,7 +933,7 @@
     <t>但我们会记得他。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Sophia; 层级=83</t>
+    <t>源类型=type:txt_Sophia; 层级=84</t>
   </si>
   <si>
     <t>89</t>
@@ -939,7 +942,7 @@
     <t>索菲亚拖着虚软的双腿向前迈了一步，手中紧握着那把曾夺去恩师性命的枪械。在承受了与导师生离死别的剧痛后，她终于积攒起直面这个拥有与盖曼相同面容的恶魔的勇气。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=84</t>
+    <t>源类型=type:txt_pb; 层级=85</t>
   </si>
   <si>
     <t>90</t>
@@ -948,7 +951,7 @@
     <t>每一个在这片梦境里受害、牺牲的人，都会在真相大白的那一刻迎来属于他们的昭雪。他们的故事需要有人来铭记，而你......会葬身在这里，和你制造的噩梦一起。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Sophia; 层级=85</t>
+    <t>源类型=type:txt_Sophia; 层级=86</t>
   </si>
   <si>
     <t>91</t>
@@ -957,7 +960,7 @@
     <t>那双青蓝色的眼睛里燃着和当初盖曼拒绝和他合作时，如出一辙的决绝，让亚波伦原本带着蛊惑的笑意僵在了嘴角。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=86</t>
+    <t>源类型=type:txt_pb; 层级=87</t>
   </si>
   <si>
     <t>92</t>
@@ -966,7 +969,7 @@
     <t>这是他此生第三次感受到名为盛怒的情绪——第一次是发现自己被纳丁达克欺骗、第二次是被意识中的盖曼拒绝。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=87</t>
+    <t>源类型=type:txt_pb; 层级=88</t>
   </si>
   <si>
     <t>93</t>
@@ -975,7 +978,7 @@
     <t>而着最后一次——便是被这个本该任他拿捏的小姑娘，顶着和她老师一样令人生厌的眼神，让他重获自由的机会眼睁睁地在他面前一点点流逝。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=88</t>
+    <t>源类型=type:txt_pb; 层级=89</t>
   </si>
   <si>
     <t>94</t>
@@ -984,7 +987,7 @@
     <t>你这不知天高地厚的蠢材！</t>
   </si>
   <si>
-    <t>源类型=type:txt_Abaddon; 层级=89</t>
+    <t>源类型=type:txt_Abaddon; 层级=90</t>
   </si>
   <si>
     <t>95</t>
@@ -994,7 +997,7 @@
   </si>
   <si>
     <r>
-      <t>bgfade(sntzm_gy(s2)_95,1)&amp;loadScript(</t>
+      <t>bgfade(sntzm_gy(s2)_95,1)&amp;playsfx(GunShot)&amp;loadScript(</t>
     </r>
     <r>
       <rPr>
@@ -1002,7 +1005,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>真结局分支</t>
+      <t>sntzm_truth(1)</t>
     </r>
     <r>
       <rPr>
@@ -1014,7 +1017,39 @@
     </r>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=90; gotomainline=真结局分支_1</t>
+    <t>源类型=type:txt_pb; 层级=91; gotomainline=真结局分支_1</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_gy(ns2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 92)</t>
+    </r>
+  </si>
+  <si>
+    <t>源类型=type:txt_Abaddon; 层级=83; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"3","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=盖亚之心（无索菲亚线下）_92</t>
   </si>
   <si>
     <t>64</t>
@@ -1026,6 +1061,18 @@
     <t>再结合那两台电刑椅彼此相连的线路，和大卫被抓后如同被催眠一般的长时间昏迷。一个可怕的猜想顿时在你脑海中勾勒出清晰的轮廓——或许当时连接着两人的设备并不只是电刑椅，而是亚波伦用来转移意识的设备。</t>
   </si>
   <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>他？你指的是谁？</t>
+  </si>
+  <si>
+    <t>jump(51)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=48; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"3","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=51</t>
+  </si>
+  <si>
     <t>项目</t>
   </si>
   <si>
@@ -1035,13 +1082,13 @@
     <t>源 JSON</t>
   </si>
   <si>
-    <t>圣诺汀之梦_盖亚之心（索菲亚线下）.json</t>
+    <t>圣诺汀之梦_盖亚之心（索菲亚线下） (1).json</t>
   </si>
   <si>
     <t>转换时间</t>
   </si>
   <si>
-    <t>2026/9/10 09:06:18</t>
+    <t>2026/9/11 11:50:12</t>
   </si>
   <si>
     <t>输出节点数</t>
@@ -1063,6 +1110,9 @@
   </si>
   <si>
     <t>说话人映射数</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>规则</t>
@@ -2756,7 +2806,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3833,12 +3883,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="29" ht="40.5" spans="1:12">
+    <row r="29" ht="27" spans="1:12">
       <c r="A29" t="s">
         <v>107</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
@@ -3876,7 +3926,7 @@
         <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -3909,7 +3959,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" ht="27" spans="1:12">
+    <row r="31" ht="54" spans="1:12">
       <c r="A31" t="s">
         <v>113</v>
       </c>
@@ -3947,18 +3997,18 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" ht="54" spans="1:12">
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>116</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -3967,7 +4017,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3979,24 +4029,24 @@
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="L32" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4005,7 +4055,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4017,7 +4067,7 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="L33" t="s">
         <v>124</v>
@@ -4028,13 +4078,13 @@
         <v>125</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4061,18 +4111,18 @@
         <v>127</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" ht="57" spans="1:12">
       <c r="A35" t="s">
         <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4093,24 +4143,24 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="L35" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="36" ht="57" spans="1:12">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" ht="27" spans="1:12">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4119,7 +4169,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4131,30 +4181,30 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="L36" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="37" ht="27" spans="1:12">
-      <c r="A37" t="s">
-        <v>135</v>
-      </c>
-      <c r="B37" t="s">
-        <v>136</v>
-      </c>
-      <c r="C37" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" t="s">
-        <v>137</v>
-      </c>
       <c r="E37" t="s">
         <v>15</v>
       </c>
       <c r="F37" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="G37" t="s">
         <v>138</v>
@@ -4169,33 +4219,33 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="L37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
       </c>
       <c r="F38" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G38" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4207,15 +4257,15 @@
         <v>15</v>
       </c>
       <c r="K38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L38" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="39" ht="40.5" spans="1:12">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4223,15 +4273,17 @@
       <c r="C39" t="s">
         <v>14</v>
       </c>
-      <c r="D39"/>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
       <c r="E39" t="s">
         <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4243,15 +4295,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L39" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" ht="67.5" spans="1:12">
       <c r="A40" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4269,7 +4321,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4281,18 +4333,18 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L40" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="41" ht="67.5" spans="1:12">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -4307,7 +4359,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4319,18 +4371,18 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="L41" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" ht="40.5" spans="1:12">
       <c r="A42" t="s">
         <v>156</v>
       </c>
       <c r="B42" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
@@ -4401,18 +4453,18 @@
         <v>161</v>
       </c>
     </row>
-    <row r="44" ht="40.5" spans="1:12">
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
         <v>162</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4433,24 +4485,24 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="L44" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
         <v>165</v>
       </c>
       <c r="B45" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4471,24 +4523,24 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="L45" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="46" ht="40.5" spans="1:12">
+    <row r="46" ht="27" spans="1:12">
       <c r="A46" t="s">
         <v>168</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4515,18 +4567,18 @@
         <v>170</v>
       </c>
     </row>
-    <row r="47" ht="27" spans="1:12">
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
         <v>171</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4553,18 +4605,18 @@
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
         <v>174</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4591,18 +4643,18 @@
         <v>176</v>
       </c>
     </row>
-    <row r="49" ht="40.5" spans="1:12">
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
         <v>177</v>
       </c>
       <c r="B49" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4611,65 +4663,65 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" t="s">
+        <v>15</v>
+      </c>
+      <c r="J49" t="s">
+        <v>15</v>
+      </c>
+      <c r="K49" t="s">
+        <v>15</v>
+      </c>
+      <c r="L49" t="s">
         <v>178</v>
-      </c>
-      <c r="H49" t="s">
-        <v>15</v>
-      </c>
-      <c r="I49" t="s">
-        <v>15</v>
-      </c>
-      <c r="J49" t="s">
-        <v>15</v>
-      </c>
-      <c r="K49" t="s">
-        <v>15</v>
-      </c>
-      <c r="L49" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="50" ht="30" spans="1:12">
       <c r="A50" t="s">
+        <v>179</v>
+      </c>
+      <c r="B50" t="s">
         <v>180</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" t="s">
         <v>181</v>
       </c>
-      <c r="C50" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" t="s">
-        <v>121</v>
-      </c>
-      <c r="E50" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>182</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" t="s">
+        <v>15</v>
+      </c>
+      <c r="K50" t="s">
+        <v>139</v>
+      </c>
+      <c r="L50" t="s">
         <v>183</v>
-      </c>
-      <c r="H50" t="s">
-        <v>15</v>
-      </c>
-      <c r="I50" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" t="s">
-        <v>15</v>
-      </c>
-      <c r="K50" t="s">
-        <v>142</v>
-      </c>
-      <c r="L50" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4684,30 +4736,30 @@
         <v>15</v>
       </c>
       <c r="F51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G51" t="s">
+        <v>185</v>
+      </c>
+      <c r="H51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" t="s">
+        <v>15</v>
+      </c>
+      <c r="K51" t="s">
         <v>186</v>
       </c>
-      <c r="H51" t="s">
-        <v>15</v>
-      </c>
-      <c r="I51" t="s">
-        <v>15</v>
-      </c>
-      <c r="J51" t="s">
-        <v>15</v>
-      </c>
-      <c r="K51" t="s">
+      <c r="L51" t="s">
         <v>187</v>
-      </c>
-      <c r="L51" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="52" ht="67.5" spans="1:12">
       <c r="A52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4725,27 +4777,27 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
+        <v>189</v>
+      </c>
+      <c r="H52" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" t="s">
+        <v>15</v>
+      </c>
+      <c r="J52" t="s">
+        <v>15</v>
+      </c>
+      <c r="K52" t="s">
         <v>190</v>
       </c>
-      <c r="H52" t="s">
-        <v>15</v>
-      </c>
-      <c r="I52" t="s">
-        <v>15</v>
-      </c>
-      <c r="J52" t="s">
-        <v>15</v>
-      </c>
-      <c r="K52" t="s">
+      <c r="L52" t="s">
         <v>191</v>
-      </c>
-      <c r="L52" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="53" ht="55.5" spans="1:12">
       <c r="A53" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4763,27 +4815,27 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
+        <v>193</v>
+      </c>
+      <c r="H53" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" t="s">
+        <v>15</v>
+      </c>
+      <c r="J53" t="s">
+        <v>15</v>
+      </c>
+      <c r="K53" t="s">
+        <v>15</v>
+      </c>
+      <c r="L53" t="s">
         <v>194</v>
-      </c>
-      <c r="H53" t="s">
-        <v>15</v>
-      </c>
-      <c r="I53" t="s">
-        <v>15</v>
-      </c>
-      <c r="J53" t="s">
-        <v>15</v>
-      </c>
-      <c r="K53" t="s">
-        <v>15</v>
-      </c>
-      <c r="L53" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="54" ht="69" spans="1:12">
       <c r="A54" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4801,65 +4853,65 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
+        <v>196</v>
+      </c>
+      <c r="H54" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" t="s">
+        <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54" t="s">
         <v>197</v>
       </c>
-      <c r="H54" t="s">
-        <v>15</v>
-      </c>
-      <c r="I54" t="s">
-        <v>15</v>
-      </c>
-      <c r="J54" t="s">
-        <v>15</v>
-      </c>
-      <c r="K54" t="s">
+      <c r="L54" t="s">
         <v>198</v>
-      </c>
-      <c r="L54" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="55" ht="27" spans="1:12">
       <c r="A55" t="s">
+        <v>199</v>
+      </c>
+      <c r="B55" t="s">
         <v>200</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s">
         <v>201</v>
       </c>
-      <c r="C55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D55" t="s">
-        <v>15</v>
-      </c>
-      <c r="E55" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" t="s">
+        <v>15</v>
+      </c>
+      <c r="J55" t="s">
+        <v>15</v>
+      </c>
+      <c r="K55" t="s">
+        <v>15</v>
+      </c>
+      <c r="L55" t="s">
         <v>202</v>
-      </c>
-      <c r="H55" t="s">
-        <v>15</v>
-      </c>
-      <c r="I55" t="s">
-        <v>15</v>
-      </c>
-      <c r="J55" t="s">
-        <v>15</v>
-      </c>
-      <c r="K55" t="s">
-        <v>15</v>
-      </c>
-      <c r="L55" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="56" ht="54" spans="1:12">
       <c r="A56" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4877,65 +4929,65 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
+        <v>204</v>
+      </c>
+      <c r="H56" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" t="s">
+        <v>15</v>
+      </c>
+      <c r="J56" t="s">
+        <v>15</v>
+      </c>
+      <c r="K56" t="s">
+        <v>15</v>
+      </c>
+      <c r="L56" t="s">
         <v>205</v>
-      </c>
-      <c r="H56" t="s">
-        <v>15</v>
-      </c>
-      <c r="I56" t="s">
-        <v>15</v>
-      </c>
-      <c r="J56" t="s">
-        <v>15</v>
-      </c>
-      <c r="K56" t="s">
-        <v>15</v>
-      </c>
-      <c r="L56" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="57" ht="55.5" spans="1:12">
       <c r="A57" t="s">
+        <v>206</v>
+      </c>
+      <c r="B57" t="s">
+        <v>200</v>
+      </c>
+      <c r="C57" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s">
         <v>207</v>
       </c>
-      <c r="B57" t="s">
-        <v>201</v>
-      </c>
-      <c r="C57" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57" t="s">
-        <v>15</v>
-      </c>
-      <c r="E57" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57" t="s">
+        <v>15</v>
+      </c>
+      <c r="K57" t="s">
+        <v>15</v>
+      </c>
+      <c r="L57" t="s">
         <v>208</v>
-      </c>
-      <c r="H57" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" t="s">
-        <v>15</v>
-      </c>
-      <c r="J57" t="s">
-        <v>15</v>
-      </c>
-      <c r="K57" t="s">
-        <v>15</v>
-      </c>
-      <c r="L57" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="58" ht="27" spans="1:12">
       <c r="A58" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B58" t="s">
         <v>91</v>
@@ -4953,27 +5005,27 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
+        <v>210</v>
+      </c>
+      <c r="H58" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58" t="s">
+        <v>15</v>
+      </c>
+      <c r="L58" t="s">
         <v>211</v>
-      </c>
-      <c r="H58" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" t="s">
-        <v>15</v>
-      </c>
-      <c r="J58" t="s">
-        <v>15</v>
-      </c>
-      <c r="K58" t="s">
-        <v>15</v>
-      </c>
-      <c r="L58" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="59" ht="27" spans="1:12">
       <c r="A59" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4991,27 +5043,27 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
+        <v>213</v>
+      </c>
+      <c r="H59" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59" t="s">
+        <v>15</v>
+      </c>
+      <c r="L59" t="s">
         <v>214</v>
-      </c>
-      <c r="H59" t="s">
-        <v>15</v>
-      </c>
-      <c r="I59" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" t="s">
-        <v>15</v>
-      </c>
-      <c r="K59" t="s">
-        <v>15</v>
-      </c>
-      <c r="L59" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="60" ht="27" spans="1:12">
       <c r="A60" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -5029,65 +5081,65 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
+        <v>216</v>
+      </c>
+      <c r="H60" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" t="s">
+        <v>15</v>
+      </c>
+      <c r="J60" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60" t="s">
+        <v>15</v>
+      </c>
+      <c r="L60" t="s">
         <v>217</v>
-      </c>
-      <c r="H60" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" t="s">
-        <v>15</v>
-      </c>
-      <c r="J60" t="s">
-        <v>15</v>
-      </c>
-      <c r="K60" t="s">
-        <v>15</v>
-      </c>
-      <c r="L60" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="61" ht="70.5" spans="1:12">
       <c r="A61" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" t="s">
+        <v>200</v>
+      </c>
+      <c r="C61" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s">
         <v>219</v>
       </c>
-      <c r="B61" t="s">
-        <v>201</v>
-      </c>
-      <c r="C61" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" t="s">
+        <v>15</v>
+      </c>
+      <c r="L61" t="s">
         <v>220</v>
-      </c>
-      <c r="H61" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" t="s">
-        <v>15</v>
-      </c>
-      <c r="K61" t="s">
-        <v>15</v>
-      </c>
-      <c r="L61" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5120,12 +5172,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="63" ht="90" spans="1:12">
       <c r="A63" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5143,27 +5195,27 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
+        <v>224</v>
+      </c>
+      <c r="H63" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" t="s">
+        <v>15</v>
+      </c>
+      <c r="J63" t="s">
+        <v>15</v>
+      </c>
+      <c r="K63" t="s">
+        <v>15</v>
+      </c>
+      <c r="L63" t="s">
         <v>225</v>
-      </c>
-      <c r="H63" t="s">
-        <v>15</v>
-      </c>
-      <c r="I63" t="s">
-        <v>15</v>
-      </c>
-      <c r="J63" t="s">
-        <v>15</v>
-      </c>
-      <c r="K63" t="s">
-        <v>15</v>
-      </c>
-      <c r="L63" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="64" ht="69" spans="1:12">
       <c r="A64" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5181,27 +5233,27 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
+        <v>227</v>
+      </c>
+      <c r="H64" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" t="s">
+        <v>15</v>
+      </c>
+      <c r="J64" t="s">
+        <v>15</v>
+      </c>
+      <c r="K64" t="s">
         <v>228</v>
       </c>
-      <c r="H64" t="s">
-        <v>15</v>
-      </c>
-      <c r="I64" t="s">
-        <v>15</v>
-      </c>
-      <c r="J64" t="s">
-        <v>15</v>
-      </c>
-      <c r="K64" t="s">
+      <c r="L64" t="s">
         <v>229</v>
-      </c>
-      <c r="L64" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="65" ht="90" spans="1:12">
       <c r="A65" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5219,27 +5271,27 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
+        <v>231</v>
+      </c>
+      <c r="H65" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J65" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" t="s">
+        <v>15</v>
+      </c>
+      <c r="L65" t="s">
         <v>232</v>
-      </c>
-      <c r="H65" t="s">
-        <v>15</v>
-      </c>
-      <c r="I65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J65" t="s">
-        <v>15</v>
-      </c>
-      <c r="K65" t="s">
-        <v>15</v>
-      </c>
-      <c r="L65" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="66" ht="69" spans="1:12">
       <c r="A66" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5257,7 +5309,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5269,15 +5321,15 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
+        <v>228</v>
+      </c>
+      <c r="L66" t="s">
         <v>229</v>
-      </c>
-      <c r="L66" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5295,27 +5347,27 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
+        <v>236</v>
+      </c>
+      <c r="H67" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" t="s">
+        <v>15</v>
+      </c>
+      <c r="J67" t="s">
+        <v>15</v>
+      </c>
+      <c r="K67" t="s">
+        <v>15</v>
+      </c>
+      <c r="L67" t="s">
         <v>237</v>
-      </c>
-      <c r="H67" t="s">
-        <v>15</v>
-      </c>
-      <c r="I67" t="s">
-        <v>15</v>
-      </c>
-      <c r="J67" t="s">
-        <v>15</v>
-      </c>
-      <c r="K67" t="s">
-        <v>15</v>
-      </c>
-      <c r="L67" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B68" t="s">
         <v>91</v>
@@ -5333,27 +5385,27 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
+        <v>239</v>
+      </c>
+      <c r="H68" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" t="s">
+        <v>15</v>
+      </c>
+      <c r="J68" t="s">
+        <v>15</v>
+      </c>
+      <c r="K68" t="s">
+        <v>15</v>
+      </c>
+      <c r="L68" t="s">
         <v>240</v>
-      </c>
-      <c r="H68" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" t="s">
-        <v>15</v>
-      </c>
-      <c r="J68" t="s">
-        <v>15</v>
-      </c>
-      <c r="K68" t="s">
-        <v>15</v>
-      </c>
-      <c r="L68" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="69" ht="27" spans="1:12">
       <c r="A69" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5371,103 +5423,103 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
+        <v>242</v>
+      </c>
+      <c r="H69" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" t="s">
+        <v>15</v>
+      </c>
+      <c r="J69" t="s">
+        <v>15</v>
+      </c>
+      <c r="K69" t="s">
+        <v>15</v>
+      </c>
+      <c r="L69" t="s">
         <v>243</v>
-      </c>
-      <c r="H69" t="s">
-        <v>15</v>
-      </c>
-      <c r="I69" t="s">
-        <v>15</v>
-      </c>
-      <c r="J69" t="s">
-        <v>15</v>
-      </c>
-      <c r="K69" t="s">
-        <v>15</v>
-      </c>
-      <c r="L69" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="70" ht="40.5" spans="1:12">
       <c r="A70" t="s">
+        <v>244</v>
+      </c>
+      <c r="B70" t="s">
+        <v>200</v>
+      </c>
+      <c r="C70" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" t="s">
+        <v>15</v>
+      </c>
+      <c r="F70" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s">
         <v>245</v>
       </c>
-      <c r="B70" t="s">
-        <v>201</v>
-      </c>
-      <c r="C70" t="s">
-        <v>14</v>
-      </c>
-      <c r="D70" t="s">
-        <v>15</v>
-      </c>
-      <c r="E70" t="s">
-        <v>15</v>
-      </c>
-      <c r="F70" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" t="s">
+        <v>15</v>
+      </c>
+      <c r="J70" t="s">
+        <v>15</v>
+      </c>
+      <c r="K70" t="s">
+        <v>15</v>
+      </c>
+      <c r="L70" t="s">
         <v>246</v>
-      </c>
-      <c r="H70" t="s">
-        <v>15</v>
-      </c>
-      <c r="I70" t="s">
-        <v>15</v>
-      </c>
-      <c r="J70" t="s">
-        <v>15</v>
-      </c>
-      <c r="K70" t="s">
-        <v>15</v>
-      </c>
-      <c r="L70" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="71" ht="55.5" spans="1:12">
       <c r="A71" t="s">
+        <v>247</v>
+      </c>
+      <c r="B71" t="s">
+        <v>200</v>
+      </c>
+      <c r="C71" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" t="s">
         <v>248</v>
       </c>
-      <c r="B71" t="s">
-        <v>201</v>
-      </c>
-      <c r="C71" t="s">
-        <v>14</v>
-      </c>
-      <c r="D71" t="s">
-        <v>15</v>
-      </c>
-      <c r="E71" t="s">
-        <v>15</v>
-      </c>
-      <c r="F71" t="s">
-        <v>15</v>
-      </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" t="s">
+        <v>15</v>
+      </c>
+      <c r="J71" t="s">
+        <v>15</v>
+      </c>
+      <c r="K71" t="s">
+        <v>15</v>
+      </c>
+      <c r="L71" t="s">
         <v>249</v>
-      </c>
-      <c r="H71" t="s">
-        <v>15</v>
-      </c>
-      <c r="I71" t="s">
-        <v>15</v>
-      </c>
-      <c r="J71" t="s">
-        <v>15</v>
-      </c>
-      <c r="K71" t="s">
-        <v>15</v>
-      </c>
-      <c r="L71" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="72" ht="54" spans="1:12">
       <c r="A72" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5485,103 +5537,103 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
+        <v>251</v>
+      </c>
+      <c r="H72" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" t="s">
+        <v>15</v>
+      </c>
+      <c r="J72" t="s">
+        <v>15</v>
+      </c>
+      <c r="K72" t="s">
+        <v>15</v>
+      </c>
+      <c r="L72" t="s">
         <v>252</v>
-      </c>
-      <c r="H72" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" t="s">
-        <v>15</v>
-      </c>
-      <c r="J72" t="s">
-        <v>15</v>
-      </c>
-      <c r="K72" t="s">
-        <v>15</v>
-      </c>
-      <c r="L72" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="73" ht="40.5" spans="1:12">
       <c r="A73" t="s">
+        <v>253</v>
+      </c>
+      <c r="B73" t="s">
+        <v>200</v>
+      </c>
+      <c r="C73" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" t="s">
+        <v>15</v>
+      </c>
+      <c r="E73" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" t="s">
         <v>254</v>
       </c>
-      <c r="B73" t="s">
-        <v>201</v>
-      </c>
-      <c r="C73" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" t="s">
-        <v>15</v>
-      </c>
-      <c r="E73" t="s">
-        <v>15</v>
-      </c>
-      <c r="F73" t="s">
-        <v>15</v>
-      </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" t="s">
+        <v>15</v>
+      </c>
+      <c r="J73" t="s">
+        <v>15</v>
+      </c>
+      <c r="K73" t="s">
+        <v>15</v>
+      </c>
+      <c r="L73" t="s">
         <v>255</v>
-      </c>
-      <c r="H73" t="s">
-        <v>15</v>
-      </c>
-      <c r="I73" t="s">
-        <v>15</v>
-      </c>
-      <c r="J73" t="s">
-        <v>15</v>
-      </c>
-      <c r="K73" t="s">
-        <v>15</v>
-      </c>
-      <c r="L73" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="74" ht="43.5" spans="1:12">
       <c r="A74" t="s">
+        <v>256</v>
+      </c>
+      <c r="B74" t="s">
+        <v>200</v>
+      </c>
+      <c r="C74" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" t="s">
         <v>257</v>
       </c>
-      <c r="B74" t="s">
-        <v>201</v>
-      </c>
-      <c r="C74" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E74" t="s">
-        <v>15</v>
-      </c>
-      <c r="F74" t="s">
-        <v>15</v>
-      </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" t="s">
+        <v>15</v>
+      </c>
+      <c r="J74" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" t="s">
+        <v>15</v>
+      </c>
+      <c r="L74" t="s">
         <v>258</v>
-      </c>
-      <c r="H74" t="s">
-        <v>15</v>
-      </c>
-      <c r="I74" t="s">
-        <v>15</v>
-      </c>
-      <c r="J74" t="s">
-        <v>15</v>
-      </c>
-      <c r="K74" t="s">
-        <v>15</v>
-      </c>
-      <c r="L74" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="75" ht="40.5" spans="1:12">
       <c r="A75" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5599,103 +5651,103 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
+        <v>260</v>
+      </c>
+      <c r="H75" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" t="s">
+        <v>15</v>
+      </c>
+      <c r="J75" t="s">
+        <v>15</v>
+      </c>
+      <c r="K75" t="s">
+        <v>15</v>
+      </c>
+      <c r="L75" t="s">
         <v>261</v>
-      </c>
-      <c r="H75" t="s">
-        <v>15</v>
-      </c>
-      <c r="I75" t="s">
-        <v>15</v>
-      </c>
-      <c r="J75" t="s">
-        <v>15</v>
-      </c>
-      <c r="K75" t="s">
-        <v>15</v>
-      </c>
-      <c r="L75" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
+        <v>262</v>
+      </c>
+      <c r="B76" t="s">
+        <v>117</v>
+      </c>
+      <c r="C76" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" t="s">
         <v>263</v>
       </c>
-      <c r="B76" t="s">
-        <v>120</v>
-      </c>
-      <c r="C76" t="s">
-        <v>14</v>
-      </c>
-      <c r="D76" t="s">
-        <v>15</v>
-      </c>
-      <c r="E76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F76" t="s">
-        <v>15</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" t="s">
+        <v>15</v>
+      </c>
+      <c r="J76" t="s">
+        <v>15</v>
+      </c>
+      <c r="K76" t="s">
         <v>264</v>
       </c>
-      <c r="H76" t="s">
-        <v>15</v>
-      </c>
-      <c r="I76" t="s">
-        <v>15</v>
-      </c>
-      <c r="J76" t="s">
-        <v>15</v>
-      </c>
-      <c r="K76" t="s">
+      <c r="L76" t="s">
         <v>265</v>
-      </c>
-      <c r="L76" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
+        <v>266</v>
+      </c>
+      <c r="B77" t="s">
+        <v>200</v>
+      </c>
+      <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s">
         <v>267</v>
       </c>
-      <c r="B77" t="s">
-        <v>201</v>
-      </c>
-      <c r="C77" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" t="s">
-        <v>15</v>
-      </c>
-      <c r="E77" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" t="s">
-        <v>15</v>
-      </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
+      <c r="L77" t="s">
         <v>268</v>
-      </c>
-      <c r="H77" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" t="s">
-        <v>15</v>
-      </c>
-      <c r="J77" t="s">
-        <v>15</v>
-      </c>
-      <c r="K77" t="s">
-        <v>15</v>
-      </c>
-      <c r="L77" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="78" ht="54" spans="1:12">
       <c r="A78" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5713,103 +5765,103 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
+        <v>270</v>
+      </c>
+      <c r="H78" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" t="s">
+        <v>15</v>
+      </c>
+      <c r="L78" t="s">
         <v>271</v>
-      </c>
-      <c r="H78" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" t="s">
-        <v>15</v>
-      </c>
-      <c r="J78" t="s">
-        <v>15</v>
-      </c>
-      <c r="K78" t="s">
-        <v>15</v>
-      </c>
-      <c r="L78" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="79" ht="54" spans="1:12">
       <c r="A79" t="s">
+        <v>272</v>
+      </c>
+      <c r="B79" t="s">
+        <v>117</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" t="s">
+        <v>15</v>
+      </c>
+      <c r="F79" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" t="s">
+        <v>270</v>
+      </c>
+      <c r="H79" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" t="s">
+        <v>15</v>
+      </c>
+      <c r="J79" t="s">
+        <v>15</v>
+      </c>
+      <c r="K79" t="s">
+        <v>15</v>
+      </c>
+      <c r="L79" t="s">
         <v>273</v>
-      </c>
-      <c r="B79" t="s">
-        <v>120</v>
-      </c>
-      <c r="C79" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" t="s">
-        <v>15</v>
-      </c>
-      <c r="E79" t="s">
-        <v>15</v>
-      </c>
-      <c r="F79" t="s">
-        <v>15</v>
-      </c>
-      <c r="G79" t="s">
-        <v>271</v>
-      </c>
-      <c r="H79" t="s">
-        <v>15</v>
-      </c>
-      <c r="I79" t="s">
-        <v>15</v>
-      </c>
-      <c r="J79" t="s">
-        <v>15</v>
-      </c>
-      <c r="K79" t="s">
-        <v>15</v>
-      </c>
-      <c r="L79" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="80" ht="42" spans="1:12">
       <c r="A80" t="s">
+        <v>274</v>
+      </c>
+      <c r="B80" t="s">
+        <v>117</v>
+      </c>
+      <c r="C80" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" t="s">
+        <v>15</v>
+      </c>
+      <c r="E80" t="s">
+        <v>15</v>
+      </c>
+      <c r="F80" t="s">
+        <v>15</v>
+      </c>
+      <c r="G80" t="s">
         <v>275</v>
       </c>
-      <c r="B80" t="s">
-        <v>120</v>
-      </c>
-      <c r="C80" t="s">
-        <v>14</v>
-      </c>
-      <c r="D80" t="s">
-        <v>15</v>
-      </c>
-      <c r="E80" t="s">
-        <v>15</v>
-      </c>
-      <c r="F80" t="s">
-        <v>15</v>
-      </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" t="s">
+        <v>15</v>
+      </c>
+      <c r="J80" t="s">
+        <v>15</v>
+      </c>
+      <c r="K80" t="s">
+        <v>15</v>
+      </c>
+      <c r="L80" t="s">
         <v>276</v>
-      </c>
-      <c r="H80" t="s">
-        <v>15</v>
-      </c>
-      <c r="I80" t="s">
-        <v>15</v>
-      </c>
-      <c r="J80" t="s">
-        <v>15</v>
-      </c>
-      <c r="K80" t="s">
-        <v>15</v>
-      </c>
-      <c r="L80" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="81" ht="40.5" spans="1:12">
       <c r="A81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5827,24 +5879,27 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
+        <v>278</v>
+      </c>
+      <c r="H81" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" t="s">
+        <v>15</v>
+      </c>
+      <c r="L81" t="s">
         <v>279</v>
-      </c>
-      <c r="H81" t="s">
-        <v>15</v>
-      </c>
-      <c r="I81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J81" t="s">
-        <v>15</v>
-      </c>
-      <c r="L81" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="82" ht="67.5" spans="1:12">
       <c r="A82" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5862,65 +5917,65 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
+        <v>281</v>
+      </c>
+      <c r="H82" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" t="s">
+        <v>15</v>
+      </c>
+      <c r="K82" t="s">
+        <v>15</v>
+      </c>
+      <c r="L82" t="s">
         <v>282</v>
-      </c>
-      <c r="H82" t="s">
-        <v>15</v>
-      </c>
-      <c r="I82" t="s">
-        <v>15</v>
-      </c>
-      <c r="J82" t="s">
-        <v>15</v>
-      </c>
-      <c r="K82" t="s">
-        <v>15</v>
-      </c>
-      <c r="L82" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
+        <v>283</v>
+      </c>
+      <c r="B83" t="s">
+        <v>200</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" t="s">
         <v>284</v>
       </c>
-      <c r="B83" t="s">
-        <v>201</v>
-      </c>
-      <c r="C83" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" t="s">
-        <v>15</v>
-      </c>
-      <c r="E83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F83" t="s">
-        <v>15</v>
-      </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" t="s">
+        <v>15</v>
+      </c>
+      <c r="J83" t="s">
+        <v>15</v>
+      </c>
+      <c r="K83" t="s">
+        <v>15</v>
+      </c>
+      <c r="L83" t="s">
         <v>285</v>
-      </c>
-      <c r="H83" t="s">
-        <v>15</v>
-      </c>
-      <c r="I83" t="s">
-        <v>15</v>
-      </c>
-      <c r="J83" t="s">
-        <v>15</v>
-      </c>
-      <c r="K83" t="s">
-        <v>15</v>
-      </c>
-      <c r="L83" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="84" ht="27" spans="1:12">
       <c r="A84" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5938,252 +5993,255 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
+        <v>287</v>
+      </c>
+      <c r="H84" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" t="s">
+        <v>15</v>
+      </c>
+      <c r="K84" t="s">
+        <v>15</v>
+      </c>
+      <c r="L84" t="s">
         <v>288</v>
-      </c>
-      <c r="H84" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" t="s">
-        <v>15</v>
-      </c>
-      <c r="J84" t="s">
-        <v>15</v>
-      </c>
-      <c r="K84" t="s">
-        <v>15</v>
-      </c>
-      <c r="L84" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="85" ht="40.5" spans="1:12">
       <c r="A85" t="s">
+        <v>289</v>
+      </c>
+      <c r="B85" t="s">
+        <v>200</v>
+      </c>
+      <c r="C85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" t="s">
+        <v>15</v>
+      </c>
+      <c r="E85" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s">
         <v>290</v>
       </c>
-      <c r="B85" t="s">
-        <v>201</v>
-      </c>
-      <c r="C85" t="s">
-        <v>14</v>
-      </c>
-      <c r="D85" t="s">
-        <v>15</v>
-      </c>
-      <c r="E85" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" t="s">
-        <v>15</v>
-      </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" t="s">
+        <v>15</v>
+      </c>
+      <c r="J85" t="s">
+        <v>15</v>
+      </c>
+      <c r="K85" t="s">
+        <v>15</v>
+      </c>
+      <c r="L85" t="s">
         <v>291</v>
       </c>
-      <c r="H85" t="s">
-        <v>15</v>
-      </c>
-      <c r="I85" t="s">
-        <v>15</v>
-      </c>
-      <c r="J85" t="s">
-        <v>15</v>
-      </c>
-      <c r="K85" t="s">
-        <v>15</v>
-      </c>
-      <c r="L85" t="s">
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="86" ht="54" spans="1:12">
-      <c r="A86" t="s">
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" t="s">
+        <v>15</v>
+      </c>
+      <c r="G86" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" t="s">
+        <v>15</v>
+      </c>
+      <c r="J86" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" t="s">
+        <v>15</v>
+      </c>
+      <c r="L86" t="s">
         <v>293</v>
       </c>
-      <c r="B86" t="s">
-        <v>201</v>
-      </c>
-      <c r="C86" t="s">
-        <v>14</v>
-      </c>
-      <c r="D86" t="s">
-        <v>15</v>
-      </c>
-      <c r="E86" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" t="s">
-        <v>15</v>
-      </c>
-      <c r="G86" t="s">
+    </row>
+    <row r="87" ht="54" spans="1:12">
+      <c r="A87" t="s">
         <v>294</v>
       </c>
-      <c r="H86" t="s">
-        <v>15</v>
-      </c>
-      <c r="I86" t="s">
-        <v>15</v>
-      </c>
-      <c r="J86" t="s">
-        <v>15</v>
-      </c>
-      <c r="K86" t="s">
-        <v>15</v>
-      </c>
-      <c r="L86" t="s">
+      <c r="B87" t="s">
+        <v>200</v>
+      </c>
+      <c r="C87" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" t="s">
+        <v>15</v>
+      </c>
+      <c r="G87" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="87" ht="30" spans="1:12">
-      <c r="A87" t="s">
+      <c r="H87" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" t="s">
+        <v>15</v>
+      </c>
+      <c r="J87" t="s">
+        <v>15</v>
+      </c>
+      <c r="K87" t="s">
+        <v>15</v>
+      </c>
+      <c r="L87" t="s">
         <v>296</v>
       </c>
-      <c r="B87" t="s">
+    </row>
+    <row r="88" ht="30" spans="1:12">
+      <c r="A88" t="s">
+        <v>297</v>
+      </c>
+      <c r="B88" t="s">
+        <v>180</v>
+      </c>
+      <c r="C88" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" t="s">
         <v>181</v>
       </c>
-      <c r="C87" t="s">
-        <v>14</v>
-      </c>
-      <c r="D87" t="s">
-        <v>182</v>
-      </c>
-      <c r="E87" t="s">
-        <v>15</v>
-      </c>
-      <c r="G87" t="s">
-        <v>297</v>
-      </c>
-      <c r="H87" t="s">
-        <v>15</v>
-      </c>
-      <c r="I87" t="s">
-        <v>15</v>
-      </c>
-      <c r="J87" t="s">
-        <v>15</v>
-      </c>
-      <c r="K87" t="s">
-        <v>123</v>
-      </c>
-      <c r="L87" t="s">
+      <c r="E88" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="88" ht="54" spans="1:12">
-      <c r="A88" t="s">
+      <c r="H88" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" t="s">
+        <v>15</v>
+      </c>
+      <c r="J88" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" t="s">
+        <v>120</v>
+      </c>
+      <c r="L88" t="s">
         <v>299</v>
       </c>
-      <c r="B88" t="s">
+    </row>
+    <row r="89" ht="54" spans="1:12">
+      <c r="A89" t="s">
+        <v>300</v>
+      </c>
+      <c r="B89" t="s">
         <v>13</v>
       </c>
-      <c r="C88" t="s">
-        <v>14</v>
-      </c>
-      <c r="D88" t="s">
-        <v>182</v>
-      </c>
-      <c r="E88" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" t="s">
-        <v>15</v>
-      </c>
-      <c r="G88" t="s">
-        <v>300</v>
-      </c>
-      <c r="H88" t="s">
-        <v>15</v>
-      </c>
-      <c r="I88" t="s">
-        <v>15</v>
-      </c>
-      <c r="J88" t="s">
-        <v>15</v>
-      </c>
-      <c r="K88" t="s">
-        <v>15</v>
-      </c>
-      <c r="L88" t="s">
+      <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" t="s">
+        <v>181</v>
+      </c>
+      <c r="E89" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="89" ht="55.5" spans="1:12">
-      <c r="A89" t="s">
+      <c r="H89" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" t="s">
+        <v>15</v>
+      </c>
+      <c r="J89" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" t="s">
+        <v>15</v>
+      </c>
+      <c r="L89" t="s">
         <v>302</v>
       </c>
-      <c r="B89" t="s">
+    </row>
+    <row r="90" ht="55.5" spans="1:12">
+      <c r="A90" t="s">
+        <v>303</v>
+      </c>
+      <c r="B90" t="s">
+        <v>180</v>
+      </c>
+      <c r="C90" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" t="s">
         <v>181</v>
       </c>
-      <c r="C89" t="s">
-        <v>14</v>
-      </c>
-      <c r="D89" t="s">
-        <v>182</v>
-      </c>
-      <c r="E89" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" t="s">
-        <v>15</v>
-      </c>
-      <c r="G89" t="s">
-        <v>303</v>
-      </c>
-      <c r="H89" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" t="s">
-        <v>15</v>
-      </c>
-      <c r="J89" t="s">
-        <v>15</v>
-      </c>
-      <c r="K89" t="s">
-        <v>15</v>
-      </c>
-      <c r="L89" t="s">
+      <c r="E90" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" t="s">
+        <v>15</v>
+      </c>
+      <c r="G90" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="90" ht="40.5" spans="1:12">
-      <c r="A90" t="s">
+      <c r="H90" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" t="s">
+        <v>15</v>
+      </c>
+      <c r="J90" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" t="s">
+        <v>15</v>
+      </c>
+      <c r="L90" t="s">
         <v>305</v>
       </c>
-      <c r="B90" t="s">
-        <v>13</v>
-      </c>
-      <c r="C90" t="s">
-        <v>14</v>
-      </c>
-      <c r="D90" t="s">
-        <v>182</v>
-      </c>
-      <c r="E90" t="s">
-        <v>15</v>
-      </c>
-      <c r="F90" t="s">
-        <v>15</v>
-      </c>
-      <c r="G90" t="s">
+    </row>
+    <row r="91" ht="40.5" spans="1:12">
+      <c r="A91" t="s">
         <v>306</v>
-      </c>
-      <c r="H90" t="s">
-        <v>15</v>
-      </c>
-      <c r="I90" t="s">
-        <v>15</v>
-      </c>
-      <c r="J90" t="s">
-        <v>15</v>
-      </c>
-      <c r="K90" t="s">
-        <v>133</v>
-      </c>
-      <c r="L90" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="91" ht="42" spans="1:12">
-      <c r="A91" t="s">
-        <v>308</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6192,7 +6250,7 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>15</v>
+        <v>181</v>
       </c>
       <c r="E91" t="s">
         <v>15</v>
@@ -6201,7 +6259,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6213,15 +6271,15 @@
         <v>15</v>
       </c>
       <c r="K91" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="L91" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="92" ht="42" spans="1:12">
       <c r="A92" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6239,101 +6297,103 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
+        <v>310</v>
+      </c>
+      <c r="H92" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" t="s">
+        <v>15</v>
+      </c>
+      <c r="J92" t="s">
+        <v>15</v>
+      </c>
+      <c r="K92" t="s">
+        <v>15</v>
+      </c>
+      <c r="L92" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="93" ht="42" spans="1:12">
+      <c r="A93" t="s">
         <v>312</v>
       </c>
-      <c r="H92" t="s">
-        <v>15</v>
-      </c>
-      <c r="I92" t="s">
-        <v>15</v>
-      </c>
-      <c r="J92" t="s">
-        <v>15</v>
-      </c>
-      <c r="K92" t="s">
-        <v>15</v>
-      </c>
-      <c r="L92" t="s">
+      <c r="B93" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" t="s">
+        <v>15</v>
+      </c>
+      <c r="E93" t="s">
+        <v>15</v>
+      </c>
+      <c r="F93" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="93" spans="1:12">
-      <c r="A93" t="s">
+      <c r="H93" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" t="s">
+        <v>15</v>
+      </c>
+      <c r="J93" t="s">
+        <v>15</v>
+      </c>
+      <c r="K93" t="s">
+        <v>15</v>
+      </c>
+      <c r="L93" t="s">
         <v>314</v>
       </c>
-      <c r="B93" t="s">
-        <v>201</v>
-      </c>
-      <c r="C93" t="s">
-        <v>14</v>
-      </c>
-      <c r="D93" t="s">
-        <v>15</v>
-      </c>
-      <c r="E93" t="s">
-        <v>15</v>
-      </c>
-      <c r="F93" t="s">
-        <v>15</v>
-      </c>
-      <c r="G93" t="s">
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" t="s">
         <v>315</v>
       </c>
-      <c r="H93" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" t="s">
-        <v>15</v>
-      </c>
-      <c r="J93" t="s">
-        <v>15</v>
-      </c>
-      <c r="K93"/>
-      <c r="L93" t="s">
+      <c r="B94" t="s">
+        <v>200</v>
+      </c>
+      <c r="C94" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" t="s">
+        <v>15</v>
+      </c>
+      <c r="G94" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="94" ht="54" spans="1:12">
-      <c r="A94" t="s">
+      <c r="H94" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" t="s">
+        <v>15</v>
+      </c>
+      <c r="K94" t="s">
+        <v>15</v>
+      </c>
+      <c r="L94" t="s">
         <v>317</v>
       </c>
-      <c r="B94" t="s">
-        <v>13</v>
-      </c>
-      <c r="C94" t="s">
-        <v>14</v>
-      </c>
-      <c r="D94" t="s">
-        <v>15</v>
-      </c>
-      <c r="E94" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" t="s">
-        <v>15</v>
-      </c>
-      <c r="G94" t="s">
+    </row>
+    <row r="95" ht="54" spans="1:12">
+      <c r="A95" t="s">
         <v>318</v>
-      </c>
-      <c r="H94" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" t="s">
-        <v>15</v>
-      </c>
-      <c r="J94" t="s">
-        <v>15</v>
-      </c>
-      <c r="K94" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="L94" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="95" ht="90" spans="1:12">
-      <c r="A95" t="s">
-        <v>321</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6351,7 +6411,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6362,49 +6422,163 @@
       <c r="J95" t="s">
         <v>15</v>
       </c>
-      <c r="K95" t="s">
-        <v>15</v>
+      <c r="K95" s="2" t="s">
+        <v>320</v>
       </c>
       <c r="L95" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="96" ht="69" spans="1:12">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="96" ht="225" spans="1:12">
       <c r="A96" t="s">
         <v>322</v>
       </c>
       <c r="B96" t="s">
+        <v>200</v>
+      </c>
+      <c r="C96" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" t="s">
+        <v>15</v>
+      </c>
+      <c r="E96" t="s">
+        <v>15</v>
+      </c>
+      <c r="F96" t="s">
+        <v>15</v>
+      </c>
+      <c r="G96" t="s">
+        <v>295</v>
+      </c>
+      <c r="H96" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" t="s">
+        <v>15</v>
+      </c>
+      <c r="J96" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="L96" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="97" ht="90" spans="1:12">
+      <c r="A97" t="s">
+        <v>325</v>
+      </c>
+      <c r="B97" t="s">
         <v>13</v>
       </c>
-      <c r="C96" t="s">
-        <v>14</v>
-      </c>
-      <c r="D96" t="s">
-        <v>15</v>
-      </c>
-      <c r="E96" t="s">
-        <v>15</v>
-      </c>
-      <c r="F96" t="s">
-        <v>15</v>
-      </c>
-      <c r="G96" t="s">
-        <v>323</v>
-      </c>
-      <c r="H96" t="s">
-        <v>15</v>
-      </c>
-      <c r="I96" t="s">
-        <v>15</v>
-      </c>
-      <c r="J96" t="s">
-        <v>15</v>
-      </c>
-      <c r="K96" t="s">
+      <c r="C97" t="s">
+        <v>14</v>
+      </c>
+      <c r="D97" t="s">
+        <v>15</v>
+      </c>
+      <c r="E97" t="s">
+        <v>15</v>
+      </c>
+      <c r="F97" t="s">
+        <v>15</v>
+      </c>
+      <c r="G97" t="s">
+        <v>231</v>
+      </c>
+      <c r="H97" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" t="s">
+        <v>15</v>
+      </c>
+      <c r="J97" t="s">
+        <v>15</v>
+      </c>
+      <c r="K97" t="s">
+        <v>15</v>
+      </c>
+      <c r="L97" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="98" ht="69" spans="1:12">
+      <c r="A98" t="s">
+        <v>326</v>
+      </c>
+      <c r="B98" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" t="s">
+        <v>15</v>
+      </c>
+      <c r="F98" t="s">
+        <v>15</v>
+      </c>
+      <c r="G98" t="s">
+        <v>327</v>
+      </c>
+      <c r="H98" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" t="s">
+        <v>15</v>
+      </c>
+      <c r="J98" t="s">
+        <v>15</v>
+      </c>
+      <c r="K98" t="s">
+        <v>228</v>
+      </c>
+      <c r="L98" t="s">
         <v>229</v>
       </c>
-      <c r="L96" t="s">
-        <v>230</v>
+    </row>
+    <row r="99" ht="210" spans="1:12">
+      <c r="A99" t="s">
+        <v>328</v>
+      </c>
+      <c r="B99" t="s">
+        <v>91</v>
+      </c>
+      <c r="C99" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" t="s">
+        <v>15</v>
+      </c>
+      <c r="E99" t="s">
+        <v>15</v>
+      </c>
+      <c r="F99" t="s">
+        <v>15</v>
+      </c>
+      <c r="G99" t="s">
+        <v>329</v>
+      </c>
+      <c r="H99" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" t="s">
+        <v>15</v>
+      </c>
+      <c r="J99" t="s">
+        <v>15</v>
+      </c>
+      <c r="K99" t="s">
+        <v>330</v>
+      </c>
+      <c r="L99" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -6425,122 +6599,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" ht="43.5" spans="1:2">
       <c r="A2" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B2" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B5" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B10" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B11" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B12" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B13" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B14" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B15" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -6562,616 +6736,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B2" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C2" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D2" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="E2" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="F2" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B3" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C3" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D3" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="E3" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="F3" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B4" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C4" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="D4" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="E4" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="F4" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B5" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="C5" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="D5" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="E5" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F5" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B6" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C6" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="D6" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="E6" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="F6" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B7" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C7" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="D7" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E7" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F7" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B8" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C8" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="D8" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="E8" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="F8" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B9" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="C9" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="D9" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="E9" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="F9" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B10" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="C10" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D10" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="E10" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F10" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B11" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="C11" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="D11" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="E11" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="F11" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B12" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C12" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="D12" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="E12" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="F12" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B13" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="C13" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="D13" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="E13" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="F13" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B14" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="C14" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="D14" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="E14" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="F14" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B15" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C15" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="D15" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="E15" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="F15" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B16" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C16" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D16" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="E16" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="F16" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B17" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C17" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="D17" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="E17" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="F17" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B18" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="C18" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="D18" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="E18" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F18" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B19" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="C19" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="D19" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="E19" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="F19" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B20" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="C20" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="D20" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="E20" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F20" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B21" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="C21" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="D21" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="E21" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="F21" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B22" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="C22" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="D22" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="E22" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="F22" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B23" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="C23" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="D23" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="E23" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="F23" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B24" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C24" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="D24" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="E24" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F24" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B25" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="C25" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="D25" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="E25" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="F25" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B26" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="C26" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="D26" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="E26" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="F26" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B27" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="C27" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="D27" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="E27" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F27" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B28" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="C28" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="D28" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="E28" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="F28" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B29" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="C29" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="D29" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="E29" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="F29" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B30" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="C30" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="D30" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="E30" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="F30" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="B31" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="C31" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="D31" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(s2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(s2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_盖亚之心（索菲亚线下） (1)" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="514">
   <si>
     <t>ID</t>
   </si>
@@ -345,6 +345,9 @@
     <t>克拉克已经躺入了其中的一台，戴上了头盔，却没有立刻按下那个红色的启动按钮，而是等你一起做好返回现实的准备。但有一个人却没有跟过来——大卫仍站在盖曼倒下去的地方，背对着出口的方向，身影立在跳动的火光里。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=25</t>
   </si>
   <si>
@@ -372,6 +375,9 @@
     <t>只见他站在离你们几步远的位置，目光正落在那片火焰上方，像是盯着某个正在缓慢成形的东西。</t>
   </si>
   <si>
+    <t>17 enhanced_suspense-tense-background-music</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=28</t>
   </si>
   <si>
@@ -642,6 +648,9 @@
     <t>大卫，你这是什么意思？放着好好的命不要，非得和我玩什么同归于尽的幼稚戏码？</t>
   </si>
   <si>
+    <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Abaddon; 层级=53</t>
   </si>
   <si>
@@ -732,7 +741,70 @@
     <t>你的思绪在这一连串问题的炮轰下，迅速飘回到十几分钟前。当你亲自按下那个处刑亚波伦的开关，看着他在电刑椅上消散之时，他的遗言不是不甘心的诅咒或哀嚎，而是“我自由了。”</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=61; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=61; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>端详飞蛾（克拉克）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视飞蛾（克拉克）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    </r>
   </si>
   <si>
     <t>66</t>
@@ -852,12 +924,6 @@
     <t>源类型=type:txt_pb; 层级=74</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=75</t>
-  </si>
-  <si>
     <t>81</t>
   </si>
   <si>
@@ -933,6 +999,12 @@
     <t>但我们会记得他。</t>
   </si>
   <si>
+    <t>19 enhanced_suspense-tension-background-music</t>
+  </si>
+  <si>
+    <t>charfadein(L,1)&amp;unlockmusic(Music19)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Sophia; 层级=84</t>
   </si>
   <si>
@@ -997,6 +1069,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>bgfade(sntzm_gy(s2)_95,1)&amp;playsfx(GunShot)&amp;loadScript(</t>
     </r>
     <r>
@@ -1055,6 +1132,9 @@
     <t>64</t>
   </si>
   <si>
+    <t>源类型=type:txt_pb; 层级=61; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+  </si>
+  <si>
     <t>67</t>
   </si>
   <si>
@@ -1653,6 +1733,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1805,11 +1890,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2118,31 +2198,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2151,124 +2228,130 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2806,7 +2889,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3833,7 +3916,7 @@
         <v>15</v>
       </c>
       <c r="I27" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="J27" t="s">
         <v>15</v>
@@ -3842,12 +3925,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3865,7 +3948,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3880,12 +3963,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" ht="27" spans="1:12">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
         <v>91</v>
@@ -3903,7 +3986,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3918,12 +4001,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="30" ht="27" spans="1:12">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" ht="60" spans="1:12">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3941,13 +4024,13 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
@@ -3956,12 +4039,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" ht="54" spans="1:12">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3979,7 +4062,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3994,21 +4077,21 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4017,7 +4100,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4029,15 +4112,15 @@
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4046,7 +4129,7 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4055,7 +4138,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4070,21 +4153,21 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4093,7 +4176,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4108,12 +4191,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" ht="57" spans="1:12">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4122,7 +4205,7 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4131,7 +4214,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4143,24 +4226,24 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L35" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" ht="27" spans="1:12">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4169,7 +4252,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4181,33 +4264,33 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L36" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
       </c>
       <c r="F37" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G37" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4219,15 +4302,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L37" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4242,10 +4325,10 @@
         <v>15</v>
       </c>
       <c r="F38" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4257,15 +4340,15 @@
         <v>15</v>
       </c>
       <c r="K38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4283,7 +4366,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4295,15 +4378,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L39" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" ht="67.5" spans="1:12">
       <c r="A40" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4321,7 +4404,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4333,18 +4416,18 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L40" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -4359,7 +4442,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4374,12 +4457,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" ht="40.5" spans="1:12">
       <c r="A42" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4397,7 +4480,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4412,12 +4495,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" ht="40.5" spans="1:12">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4435,7 +4518,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4450,21 +4533,21 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4473,7 +4556,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4485,15 +4568,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L44" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4502,7 +4585,7 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4511,7 +4594,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4526,21 +4609,21 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" ht="27" spans="1:12">
       <c r="A46" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4549,7 +4632,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4564,12 +4647,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4578,7 +4661,7 @@
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4587,7 +4670,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4602,21 +4685,21 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B48" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4625,7 +4708,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4640,12 +4723,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4678,30 +4761,30 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" ht="30" spans="1:12">
       <c r="A50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
       </c>
       <c r="F50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4713,15 +4796,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L50" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4736,10 +4819,10 @@
         <v>15</v>
       </c>
       <c r="F51" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G51" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4751,15 +4834,15 @@
         <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L51" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" ht="67.5" spans="1:12">
       <c r="A52" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4777,7 +4860,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4789,15 +4872,15 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L52" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53" ht="55.5" spans="1:12">
       <c r="A53" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4815,7 +4898,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4830,12 +4913,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" ht="69" spans="1:12">
       <c r="A54" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4853,7 +4936,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4865,18 +4948,18 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L54" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="55" ht="27" spans="1:12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55" ht="45" spans="1:12">
       <c r="A55" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B55" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -4891,13 +4974,13 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
       </c>
       <c r="I55" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="J55" t="s">
         <v>15</v>
@@ -4906,12 +4989,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" ht="54" spans="1:12">
       <c r="A56" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4929,7 +5012,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4944,15 +5027,15 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" ht="55.5" spans="1:12">
       <c r="A57" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B57" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4967,7 +5050,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4982,12 +5065,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="58" ht="27" spans="1:12">
       <c r="A58" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B58" t="s">
         <v>91</v>
@@ -5005,7 +5088,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5020,12 +5103,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" ht="27" spans="1:12">
       <c r="A59" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5043,7 +5126,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5058,12 +5141,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" ht="27" spans="1:12">
       <c r="A60" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -5081,7 +5164,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5096,15 +5179,15 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="61" ht="70.5" spans="1:12">
       <c r="A61" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B61" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -5119,7 +5202,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5134,12 +5217,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5172,12 +5255,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="63" ht="90" spans="1:12">
       <c r="A63" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5195,7 +5278,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5210,12 +5293,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" ht="69" spans="1:12">
       <c r="A64" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5233,7 +5316,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5245,15 +5328,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L64" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="65" ht="90" spans="1:12">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="65" ht="150" spans="1:12">
       <c r="A65" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5271,7 +5354,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5285,13 +5368,13 @@
       <c r="K65" t="s">
         <v>15</v>
       </c>
-      <c r="L65" t="s">
-        <v>232</v>
+      <c r="L65" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="66" ht="69" spans="1:12">
       <c r="A66" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5309,7 +5392,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5321,15 +5404,15 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L66" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5347,7 +5430,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5362,12 +5445,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B68" t="s">
         <v>91</v>
@@ -5385,7 +5468,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5400,12 +5483,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="69" ht="27" spans="1:12">
       <c r="A69" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5423,7 +5506,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5438,15 +5521,15 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="70" ht="40.5" spans="1:12">
       <c r="A70" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B70" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -5461,7 +5544,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5476,15 +5559,15 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="71" ht="55.5" spans="1:12">
       <c r="A71" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B71" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -5499,7 +5582,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5514,12 +5597,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="72" ht="54" spans="1:12">
       <c r="A72" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5537,7 +5620,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5552,15 +5635,15 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="73" ht="40.5" spans="1:12">
       <c r="A73" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B73" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -5575,7 +5658,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5590,15 +5673,15 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="74" ht="43.5" spans="1:12">
       <c r="A74" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B74" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -5613,7 +5696,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5628,12 +5711,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="75" ht="40.5" spans="1:12">
       <c r="A75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5651,7 +5734,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5666,15 +5749,15 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B76" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5689,7 +5772,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5701,18 +5784,18 @@
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L76" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B77" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
@@ -5727,7 +5810,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5742,12 +5825,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="78" ht="54" spans="1:12">
       <c r="A78" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5765,7 +5848,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5780,15 +5863,15 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="79" ht="54" spans="1:12">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="79" ht="42" spans="1:12">
       <c r="A79" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B79" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
@@ -5803,7 +5886,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5818,15 +5901,15 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="80" ht="42" spans="1:12">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="80" ht="40.5" spans="1:12">
       <c r="A80" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B80" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
@@ -5841,7 +5924,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5856,12 +5939,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="81" ht="40.5" spans="1:12">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="81" ht="67.5" spans="1:12">
       <c r="A81" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5879,7 +5962,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5894,54 +5977,54 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="82" ht="67.5" spans="1:12">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B82" t="s">
+        <v>202</v>
+      </c>
+      <c r="C82" t="s">
+        <v>14</v>
+      </c>
+      <c r="D82" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" t="s">
+        <v>285</v>
+      </c>
+      <c r="H82" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" t="s">
+        <v>15</v>
+      </c>
+      <c r="K82" t="s">
+        <v>15</v>
+      </c>
+      <c r="L82" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="83" ht="27" spans="1:12">
+      <c r="A83" t="s">
+        <v>287</v>
+      </c>
+      <c r="B83" t="s">
         <v>13</v>
       </c>
-      <c r="C82" t="s">
-        <v>14</v>
-      </c>
-      <c r="D82" t="s">
-        <v>15</v>
-      </c>
-      <c r="E82" t="s">
-        <v>15</v>
-      </c>
-      <c r="F82" t="s">
-        <v>15</v>
-      </c>
-      <c r="G82" t="s">
-        <v>281</v>
-      </c>
-      <c r="H82" t="s">
-        <v>15</v>
-      </c>
-      <c r="I82" t="s">
-        <v>15</v>
-      </c>
-      <c r="J82" t="s">
-        <v>15</v>
-      </c>
-      <c r="K82" t="s">
-        <v>15</v>
-      </c>
-      <c r="L82" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12">
-      <c r="A83" t="s">
-        <v>283</v>
-      </c>
-      <c r="B83" t="s">
-        <v>200</v>
-      </c>
       <c r="C83" t="s">
         <v>14</v>
       </c>
@@ -5955,7 +6038,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5970,54 +6053,54 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="84" ht="27" spans="1:12">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B84" t="s">
+        <v>202</v>
+      </c>
+      <c r="C84" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" t="s">
+        <v>291</v>
+      </c>
+      <c r="H84" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" t="s">
+        <v>15</v>
+      </c>
+      <c r="K84" t="s">
+        <v>15</v>
+      </c>
+      <c r="L84" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" t="s">
+        <v>293</v>
+      </c>
+      <c r="B85" t="s">
         <v>13</v>
       </c>
-      <c r="C84" t="s">
-        <v>14</v>
-      </c>
-      <c r="D84" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" t="s">
-        <v>15</v>
-      </c>
-      <c r="G84" t="s">
-        <v>287</v>
-      </c>
-      <c r="H84" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" t="s">
-        <v>15</v>
-      </c>
-      <c r="J84" t="s">
-        <v>15</v>
-      </c>
-      <c r="K84" t="s">
-        <v>15</v>
-      </c>
-      <c r="L84" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="85" ht="40.5" spans="1:12">
-      <c r="A85" t="s">
-        <v>289</v>
-      </c>
-      <c r="B85" t="s">
-        <v>200</v>
-      </c>
       <c r="C85" t="s">
         <v>14</v>
       </c>
@@ -6031,7 +6114,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>290</v>
+        <v>15</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6046,97 +6129,97 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="86" ht="54" spans="1:12">
       <c r="A86" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B86" t="s">
+        <v>202</v>
+      </c>
+      <c r="C86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" t="s">
+        <v>15</v>
+      </c>
+      <c r="G86" t="s">
+        <v>296</v>
+      </c>
+      <c r="H86" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" t="s">
+        <v>15</v>
+      </c>
+      <c r="J86" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" t="s">
+        <v>15</v>
+      </c>
+      <c r="L86" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="87" ht="60" spans="1:12">
+      <c r="A87" t="s">
+        <v>298</v>
+      </c>
+      <c r="B87" t="s">
+        <v>182</v>
+      </c>
+      <c r="C87" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" t="s">
+        <v>183</v>
+      </c>
+      <c r="E87" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" t="s">
+        <v>15</v>
+      </c>
+      <c r="G87" t="s">
+        <v>299</v>
+      </c>
+      <c r="H87" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" t="s">
+        <v>300</v>
+      </c>
+      <c r="J87" t="s">
+        <v>15</v>
+      </c>
+      <c r="K87" t="s">
+        <v>301</v>
+      </c>
+      <c r="L87" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="88" ht="54" spans="1:12">
+      <c r="A88" t="s">
+        <v>303</v>
+      </c>
+      <c r="B88" t="s">
         <v>13</v>
       </c>
-      <c r="C86" t="s">
-        <v>14</v>
-      </c>
-      <c r="D86" t="s">
-        <v>15</v>
-      </c>
-      <c r="E86" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" t="s">
-        <v>15</v>
-      </c>
-      <c r="G86" t="s">
-        <v>15</v>
-      </c>
-      <c r="H86" t="s">
-        <v>15</v>
-      </c>
-      <c r="I86" t="s">
-        <v>15</v>
-      </c>
-      <c r="J86" t="s">
-        <v>15</v>
-      </c>
-      <c r="K86" t="s">
-        <v>15</v>
-      </c>
-      <c r="L86" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="87" ht="54" spans="1:12">
-      <c r="A87" t="s">
-        <v>294</v>
-      </c>
-      <c r="B87" t="s">
-        <v>200</v>
-      </c>
-      <c r="C87" t="s">
-        <v>14</v>
-      </c>
-      <c r="D87" t="s">
-        <v>15</v>
-      </c>
-      <c r="E87" t="s">
-        <v>15</v>
-      </c>
-      <c r="F87" t="s">
-        <v>15</v>
-      </c>
-      <c r="G87" t="s">
-        <v>295</v>
-      </c>
-      <c r="H87" t="s">
-        <v>15</v>
-      </c>
-      <c r="I87" t="s">
-        <v>15</v>
-      </c>
-      <c r="J87" t="s">
-        <v>15</v>
-      </c>
-      <c r="K87" t="s">
-        <v>15</v>
-      </c>
-      <c r="L87" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="88" ht="30" spans="1:12">
-      <c r="A88" t="s">
-        <v>297</v>
-      </c>
-      <c r="B88" t="s">
-        <v>180</v>
-      </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -6145,7 +6228,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6157,62 +6240,62 @@
         <v>15</v>
       </c>
       <c r="K88" t="s">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="89" ht="54" spans="1:12">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="89" ht="55.5" spans="1:12">
       <c r="A89" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B89" t="s">
+        <v>182</v>
+      </c>
+      <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" t="s">
+        <v>183</v>
+      </c>
+      <c r="E89" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" t="s">
+        <v>307</v>
+      </c>
+      <c r="H89" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" t="s">
+        <v>15</v>
+      </c>
+      <c r="J89" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" t="s">
+        <v>15</v>
+      </c>
+      <c r="L89" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="90" ht="40.5" spans="1:12">
+      <c r="A90" t="s">
+        <v>309</v>
+      </c>
+      <c r="B90" t="s">
         <v>13</v>
       </c>
-      <c r="C89" t="s">
-        <v>14</v>
-      </c>
-      <c r="D89" t="s">
-        <v>181</v>
-      </c>
-      <c r="E89" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" t="s">
-        <v>15</v>
-      </c>
-      <c r="G89" t="s">
-        <v>301</v>
-      </c>
-      <c r="H89" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" t="s">
-        <v>15</v>
-      </c>
-      <c r="J89" t="s">
-        <v>15</v>
-      </c>
-      <c r="K89" t="s">
-        <v>15</v>
-      </c>
-      <c r="L89" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="90" ht="55.5" spans="1:12">
-      <c r="A90" t="s">
-        <v>303</v>
-      </c>
-      <c r="B90" t="s">
-        <v>180</v>
-      </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -6221,7 +6304,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6233,15 +6316,15 @@
         <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="L90" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="91" ht="40.5" spans="1:12">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="91" ht="60" spans="1:12">
       <c r="A91" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6250,7 +6333,7 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
       <c r="E91" t="s">
         <v>15</v>
@@ -6259,27 +6342,27 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
       </c>
       <c r="I91" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="J91" t="s">
         <v>15</v>
       </c>
       <c r="K91" t="s">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="92" ht="42" spans="1:12">
       <c r="A92" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6297,7 +6380,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6312,54 +6395,54 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="93" ht="42" spans="1:12">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B93" t="s">
+        <v>202</v>
+      </c>
+      <c r="C93" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" t="s">
+        <v>15</v>
+      </c>
+      <c r="E93" t="s">
+        <v>15</v>
+      </c>
+      <c r="F93" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" t="s">
+        <v>319</v>
+      </c>
+      <c r="H93" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" t="s">
+        <v>15</v>
+      </c>
+      <c r="J93" t="s">
+        <v>15</v>
+      </c>
+      <c r="K93" t="s">
+        <v>15</v>
+      </c>
+      <c r="L93" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="94" ht="54" spans="1:12">
+      <c r="A94" t="s">
+        <v>321</v>
+      </c>
+      <c r="B94" t="s">
         <v>13</v>
       </c>
-      <c r="C93" t="s">
-        <v>14</v>
-      </c>
-      <c r="D93" t="s">
-        <v>15</v>
-      </c>
-      <c r="E93" t="s">
-        <v>15</v>
-      </c>
-      <c r="F93" t="s">
-        <v>15</v>
-      </c>
-      <c r="G93" t="s">
-        <v>313</v>
-      </c>
-      <c r="H93" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" t="s">
-        <v>15</v>
-      </c>
-      <c r="J93" t="s">
-        <v>15</v>
-      </c>
-      <c r="K93" t="s">
-        <v>15</v>
-      </c>
-      <c r="L93" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12">
-      <c r="A94" t="s">
-        <v>315</v>
-      </c>
-      <c r="B94" t="s">
-        <v>200</v>
-      </c>
       <c r="C94" t="s">
         <v>14</v>
       </c>
@@ -6373,7 +6456,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6384,58 +6467,58 @@
       <c r="J94" t="s">
         <v>15</v>
       </c>
-      <c r="K94" t="s">
-        <v>15</v>
+      <c r="K94" s="3" t="s">
+        <v>323</v>
       </c>
       <c r="L94" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="95" ht="54" spans="1:12">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="95" ht="225" spans="1:12">
       <c r="A95" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B95" t="s">
+        <v>202</v>
+      </c>
+      <c r="C95" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" t="s">
+        <v>15</v>
+      </c>
+      <c r="E95" t="s">
+        <v>15</v>
+      </c>
+      <c r="F95" t="s">
+        <v>15</v>
+      </c>
+      <c r="G95" t="s">
+        <v>296</v>
+      </c>
+      <c r="H95" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" t="s">
+        <v>15</v>
+      </c>
+      <c r="J95" t="s">
+        <v>15</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="L95" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="96" ht="150" spans="1:12">
+      <c r="A96" t="s">
+        <v>328</v>
+      </c>
+      <c r="B96" t="s">
         <v>13</v>
       </c>
-      <c r="C95" t="s">
-        <v>14</v>
-      </c>
-      <c r="D95" t="s">
-        <v>15</v>
-      </c>
-      <c r="E95" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" t="s">
-        <v>15</v>
-      </c>
-      <c r="G95" t="s">
-        <v>319</v>
-      </c>
-      <c r="H95" t="s">
-        <v>15</v>
-      </c>
-      <c r="I95" t="s">
-        <v>15</v>
-      </c>
-      <c r="J95" t="s">
-        <v>15</v>
-      </c>
-      <c r="K95" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="L95" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="96" ht="225" spans="1:12">
-      <c r="A96" t="s">
-        <v>322</v>
-      </c>
-      <c r="B96" t="s">
-        <v>200</v>
-      </c>
       <c r="C96" t="s">
         <v>14</v>
       </c>
@@ -6449,7 +6532,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>295</v>
+        <v>234</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6460,16 +6543,16 @@
       <c r="J96" t="s">
         <v>15</v>
       </c>
-      <c r="K96" s="2" t="s">
-        <v>323</v>
+      <c r="K96" t="s">
+        <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="97" ht="90" spans="1:12">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="97" ht="69" spans="1:12">
       <c r="A97" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6487,30 +6570,30 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
+        <v>331</v>
+      </c>
+      <c r="H97" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" t="s">
+        <v>15</v>
+      </c>
+      <c r="J97" t="s">
+        <v>15</v>
+      </c>
+      <c r="K97" t="s">
         <v>231</v>
-      </c>
-      <c r="H97" t="s">
-        <v>15</v>
-      </c>
-      <c r="I97" t="s">
-        <v>15</v>
-      </c>
-      <c r="J97" t="s">
-        <v>15</v>
-      </c>
-      <c r="K97" t="s">
-        <v>15</v>
       </c>
       <c r="L97" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="98" ht="69" spans="1:12">
+    <row r="98" ht="210" spans="1:12">
       <c r="A98" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
@@ -6525,7 +6608,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6537,48 +6620,10 @@
         <v>15</v>
       </c>
       <c r="K98" t="s">
-        <v>228</v>
+        <v>334</v>
       </c>
       <c r="L98" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="99" ht="210" spans="1:12">
-      <c r="A99" t="s">
-        <v>328</v>
-      </c>
-      <c r="B99" t="s">
-        <v>91</v>
-      </c>
-      <c r="C99" t="s">
-        <v>14</v>
-      </c>
-      <c r="D99" t="s">
-        <v>15</v>
-      </c>
-      <c r="E99" t="s">
-        <v>15</v>
-      </c>
-      <c r="F99" t="s">
-        <v>15</v>
-      </c>
-      <c r="G99" t="s">
-        <v>329</v>
-      </c>
-      <c r="H99" t="s">
-        <v>15</v>
-      </c>
-      <c r="I99" t="s">
-        <v>15</v>
-      </c>
-      <c r="J99" t="s">
-        <v>15</v>
-      </c>
-      <c r="K99" t="s">
-        <v>330</v>
-      </c>
-      <c r="L99" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -6599,47 +6644,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" ht="43.5" spans="1:2">
       <c r="A2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B5" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -6647,7 +6692,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -6655,66 +6700,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B9" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B10" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B11" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B12" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B13" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B14" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B15" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -6736,616 +6781,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F4" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C5" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D5" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B6" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C6" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D6" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F6" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B7" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C7" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D7" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E7" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F7" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B8" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C8" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D8" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E8" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F8" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B9" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C9" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D9" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E9" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F9" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C10" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D10" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E10" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F10" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B11" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C11" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D11" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E11" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F11" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B12" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C12" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D12" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E12" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F12" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B13" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C13" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D13" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F13" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B14" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C14" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D14" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E14" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F14" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B15" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C15" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D15" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E15" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F15" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B16" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C16" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D16" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E16" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B17" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C17" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D17" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E17" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F17" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B18" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C18" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D18" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E18" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F18" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B19" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C19" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D19" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E19" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="F19" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B20" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C20" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D20" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E20" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F20" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B21" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C21" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D21" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E21" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F21" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B22" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C22" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D22" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E22" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F22" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B23" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C23" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D23" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E23" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F23" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B24" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C24" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D24" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E24" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="F24" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B25" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C25" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D25" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E25" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F25" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B26" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C26" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D26" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E26" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F26" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B27" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C27" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D27" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="E27" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="F27" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B28" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C28" t="s">
+        <v>497</v>
+      </c>
+      <c r="D28" t="s">
         <v>493</v>
       </c>
-      <c r="D28" t="s">
-        <v>489</v>
-      </c>
       <c r="E28" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F28" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B29" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C29" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D29" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="E29" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F29" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B30" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C30" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D30" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="E30" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F30" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B31" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C31" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D31" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
